--- a/artfynd/A 21422-2023 artfynd.xlsx
+++ b/artfynd/A 21422-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21422-2023 artfynd.xlsx
+++ b/artfynd/A 21422-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>98539361</v>
       </c>
       <c r="B2" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -734,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>673978.2380013692</v>
+        <v>673978</v>
       </c>
       <c r="R2" t="n">
-        <v>6697930.128569126</v>
+        <v>6697930</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -806,37 +801,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98538195</v>
+        <v>98539477</v>
       </c>
       <c r="B3" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -865,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>673969.6872819657</v>
+        <v>674073</v>
       </c>
       <c r="R3" t="n">
-        <v>6697911.890169702</v>
+        <v>6697958</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -940,12 +930,7 @@
         <v>98538194</v>
       </c>
       <c r="B4" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +981,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>673981.3520889496</v>
+        <v>673982</v>
       </c>
       <c r="R4" t="n">
-        <v>6697916.906468811</v>
+        <v>6697917</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1065,6 +1050,258 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>98538195</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Forsmark, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>673969</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6697912</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>00:06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-07-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>00:06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>98538198</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Forsmark, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>674030</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6697950</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>23:59</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>23:59</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21422-2023 artfynd.xlsx
+++ b/artfynd/A 21422-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539361</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539477</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538194</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538195</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1302,8 +1327,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538198</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>